--- a/resources/Factors.xlsx
+++ b/resources/Factors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ray.james.TVI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55624C1E-8E93-4126-ABB1-D987D6AFD1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698ACF0B-385D-4C59-970D-90D79205C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="25290" windowHeight="13830" xr2:uid="{84C42952-5FA7-4B7D-9BCC-33BCBAD26808}"/>
   </bookViews>
@@ -140,9 +140,6 @@
     <t>99202, 99203, 99212, 99213</t>
   </si>
   <si>
-    <t>1, 2, 3, 4, 5, or 6</t>
-  </si>
-  <si>
     <t>Code Match Value</t>
   </si>
   <si>
@@ -168,6 +165,9 @@
   </si>
   <si>
     <t>Mednet (C004)</t>
+  </si>
+  <si>
+    <t>1, 2, 3, 4, 5, 6, 91, 92, 93, 94,95, 96, 98, 99</t>
   </si>
 </sst>
 </file>
@@ -751,7 +751,7 @@
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.28515625" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
@@ -774,31 +774,31 @@
         <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" t="s">
         <v>38</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>39</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>40</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>41</v>
-      </c>
-      <c r="L1" t="s">
-        <v>42</v>
       </c>
       <c r="P1" t="s">
         <v>19</v>
@@ -930,7 +930,7 @@
         <v>28</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2">
         <v>1.3</v>
@@ -1185,7 +1185,7 @@
         <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2">
         <v>1.3</v>
@@ -1434,7 +1434,7 @@
         <v>28</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>

--- a/resources/Factors.xlsx
+++ b/resources/Factors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ray.james.TVI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698ACF0B-385D-4C59-970D-90D79205C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7991F53B-A913-444A-9EB2-6BD70C12DB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="25290" windowHeight="13830" xr2:uid="{84C42952-5FA7-4B7D-9BCC-33BCBAD26808}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="44">
   <si>
     <t>Truelife</t>
   </si>
@@ -168,13 +168,16 @@
   </si>
   <si>
     <t>1, 2, 3, 4, 5, 6, 91, 92, 93, 94,95, 96, 98, 99</t>
+  </si>
+  <si>
+    <t>96375</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +189,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -397,10 +406,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{04E560D1-0B12-4C9E-80CF-60BBBD5F00C1}" name="Factors" displayName="Factors" ref="A1:L16" totalsRowShown="0" dataDxfId="12">
-  <autoFilter ref="A1:L16" xr:uid="{04E560D1-0B12-4C9E-80CF-60BBBD5F00C1}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F16">
-    <sortCondition descending="1" ref="A1:A16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{04E560D1-0B12-4C9E-80CF-60BBBD5F00C1}" name="Factors" displayName="Factors" ref="A1:L19" totalsRowShown="0" dataDxfId="12">
+  <autoFilter ref="A1:L19" xr:uid="{04E560D1-0B12-4C9E-80CF-60BBBD5F00C1}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F19">
+    <sortCondition descending="1" ref="A1:A19"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="6" xr3:uid="{BF236755-ADFA-4882-9C7B-15DC7A047F38}" name="Facility" dataDxfId="11"/>
@@ -745,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{897F8A23-2B16-4F9C-B6EC-63C31BF2F9D9}">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
@@ -873,13 +882,13 @@
         <v>MF7003</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="5">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -924,16 +933,16 @@
         <v>MF7003</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>42</v>
+      <c r="E4" s="5">
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -975,16 +984,16 @@
         <v>MF7003</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5">
-        <v>97</v>
+      <c r="E5" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -1026,13 +1035,13 @@
         <v>MF7003</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="5">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -1064,7 +1073,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B7" s="4" t="str">
         <f>IFERROR(
@@ -1074,19 +1083,19 @@
 Facilities[Facility],0
 )
 ),"")</f>
-        <v>MF5020</v>
+        <v>MF7003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="E7" s="5">
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -1128,16 +1137,16 @@
         <v>MF5020</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="5">
-        <v>8</v>
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="F8" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -1182,13 +1191,13 @@
         <v>29</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -1230,13 +1239,13 @@
         <v>MF5020</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E10" s="5">
-        <v>97</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2">
         <v>1</v>
@@ -1281,16 +1290,16 @@
         <v>MF5020</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="5">
-        <v>7</v>
+      <c r="E11" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -1319,7 +1328,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="4" t="str">
         <f>IFERROR(
@@ -1329,19 +1338,19 @@
 Facilities[Facility],0
 )
 ),"")</f>
-        <v>MF5357</v>
+        <v>MF5020</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
+      </c>
+      <c r="E12" s="5">
+        <v>97</v>
       </c>
       <c r="F12" s="2">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -1349,16 +1358,16 @@
       <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="I12" s="2">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2">
-        <v>1</v>
-      </c>
-      <c r="L12" s="2">
+      <c r="I12" s="6">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1</v>
+      </c>
+      <c r="L12" s="6">
         <v>1</v>
       </c>
       <c r="P12" t="s">
@@ -1370,7 +1379,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="4" t="str">
         <f>IFERROR(
@@ -1380,16 +1389,16 @@
 Facilities[Facility],0
 )
 ),"")</f>
-        <v>MF5357</v>
+        <v>MF5020</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -1400,16 +1409,16 @@
       <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="I13" s="2">
-        <v>1</v>
-      </c>
-      <c r="J13" s="2">
-        <v>1</v>
-      </c>
-      <c r="K13" s="2">
-        <v>1</v>
-      </c>
-      <c r="L13" s="2">
+      <c r="I13" s="6">
+        <v>1</v>
+      </c>
+      <c r="J13" s="6">
+        <v>1</v>
+      </c>
+      <c r="K13" s="6">
+        <v>1</v>
+      </c>
+      <c r="L13" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1428,16 +1437,16 @@
         <v>MF5357</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -1473,13 +1482,13 @@
         <v>MF5357</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="5">
-        <v>97</v>
+        <v>26</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -1490,16 +1499,16 @@
       <c r="H15" s="2">
         <v>1</v>
       </c>
-      <c r="I15" s="2">
-        <v>1</v>
-      </c>
-      <c r="J15" s="2">
-        <v>1</v>
-      </c>
-      <c r="K15" s="2">
-        <v>1</v>
-      </c>
-      <c r="L15" s="2">
+      <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+      <c r="L15" s="6">
         <v>1</v>
       </c>
     </row>
@@ -1518,37 +1527,173 @@
         <v>MF5357</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="5">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" s="2">
+        <v>1</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4" t="str">
+        <f>IFERROR(
+INDEX(
+Facilities[Facility ID],
+MATCH(Factors[[#This Row],[Facility]],
+Facilities[Facility],0
+)
+),"")</f>
+        <v>MF5357</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="4" t="str">
+        <f>IFERROR(
+INDEX(
+Facilities[Facility ID],
+MATCH(Factors[[#This Row],[Facility]],
+Facilities[Facility],0
+)
+),"")</f>
+        <v>MF5357</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="5">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2">
+        <v>1</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1</v>
+      </c>
+      <c r="K18" s="2">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="4" t="str">
+        <f>IFERROR(
+INDEX(
+Facilities[Facility ID],
+MATCH(Factors[[#This Row],[Facility]],
+Facilities[Facility],0
+)
+),"")</f>
+        <v>MF5357</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="5">
         <v>7</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2">
-        <v>1</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="2">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
